--- a/minio-report-tracker/xlxs/devint1.xlsx
+++ b/minio-report-tracker/xlxs/devint1.xlsx
@@ -656,34 +656,34 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="3" customWidth="1" min="32" max="32"/>
+    <col width="3" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>494</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>323</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>322</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,167 +2316,167 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>510</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>150</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
